--- a/output/stock_quant_scores/C_info.xlsx
+++ b/output/stock_quant_scores/C_info.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FQ2"/>
+  <dimension ref="A1:FU2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1056,235 +1056,255 @@
       </c>
       <c r="DW1" s="1" t="inlineStr">
         <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="DX1" s="1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="DY1" s="1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="DZ1" s="1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="EA1" s="1" t="inlineStr">
+        <is>
+          <t>postMarketTime</t>
+        </is>
+      </c>
+      <c r="EB1" s="1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="EC1" s="1" t="inlineStr">
+        <is>
           <t>exchange</t>
         </is>
       </c>
-      <c r="DX1" s="1" t="inlineStr">
+      <c r="ED1" s="1" t="inlineStr">
         <is>
           <t>messageBoardId</t>
         </is>
       </c>
-      <c r="DY1" s="1" t="inlineStr">
+      <c r="EE1" s="1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="EF1" s="1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="EG1" s="1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="EH1" s="1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="EI1" s="1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="EJ1" s="1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="EK1" s="1" t="inlineStr">
         <is>
           <t>regularMarketPrice</t>
         </is>
       </c>
-      <c r="DZ1" s="1" t="inlineStr">
+      <c r="EL1" s="1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="EM1" s="1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="EN1" s="1" t="inlineStr">
+        <is>
+          <t>earningsCallTimestampStart</t>
+        </is>
+      </c>
+      <c r="EO1" s="1" t="inlineStr">
+        <is>
+          <t>earningsCallTimestampEnd</t>
+        </is>
+      </c>
+      <c r="EP1" s="1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="EQ1" s="1" t="inlineStr">
         <is>
           <t>epsTrailingTwelveMonths</t>
         </is>
       </c>
-      <c r="EA1" s="1" t="inlineStr">
+      <c r="ER1" s="1" t="inlineStr">
         <is>
           <t>epsForward</t>
         </is>
       </c>
-      <c r="EB1" s="1" t="inlineStr">
+      <c r="ES1" s="1" t="inlineStr">
         <is>
           <t>epsCurrentYear</t>
         </is>
       </c>
-      <c r="EC1" s="1" t="inlineStr">
+      <c r="ET1" s="1" t="inlineStr">
         <is>
           <t>priceEpsCurrentYear</t>
         </is>
       </c>
-      <c r="ED1" s="1" t="inlineStr">
+      <c r="EU1" s="1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChange</t>
         </is>
       </c>
-      <c r="EE1" s="1" t="inlineStr">
+      <c r="EV1" s="1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="EF1" s="1" t="inlineStr">
+      <c r="EW1" s="1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChange</t>
         </is>
       </c>
-      <c r="EG1" s="1" t="inlineStr">
+      <c r="EX1" s="1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="EH1" s="1" t="inlineStr">
+      <c r="EY1" s="1" t="inlineStr">
         <is>
           <t>sourceInterval</t>
         </is>
       </c>
-      <c r="EI1" s="1" t="inlineStr">
+      <c r="EZ1" s="1" t="inlineStr">
         <is>
           <t>exchangeDataDelayedBy</t>
         </is>
       </c>
-      <c r="EJ1" s="1" t="inlineStr">
+      <c r="FA1" s="1" t="inlineStr">
         <is>
           <t>averageAnalystRating</t>
         </is>
       </c>
-      <c r="EK1" s="1" t="inlineStr">
+      <c r="FB1" s="1" t="inlineStr">
         <is>
           <t>cryptoTradeable</t>
         </is>
       </c>
-      <c r="EL1" s="1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="EM1" s="1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="EN1" s="1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="EO1" s="1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="EP1" s="1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="EQ1" s="1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="ER1" s="1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="ES1" s="1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="ET1" s="1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="EU1" s="1" t="inlineStr">
+      <c r="FC1" s="1" t="inlineStr">
         <is>
           <t>hasPrePostMarketData</t>
         </is>
       </c>
-      <c r="EV1" s="1" t="inlineStr">
+      <c r="FD1" s="1" t="inlineStr">
         <is>
           <t>firstTradeDateMilliseconds</t>
         </is>
       </c>
-      <c r="EW1" s="1" t="inlineStr">
+      <c r="FE1" s="1" t="inlineStr">
+        <is>
+          <t>postMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="FF1" s="1" t="inlineStr">
+        <is>
+          <t>postMarketPrice</t>
+        </is>
+      </c>
+      <c r="FG1" s="1" t="inlineStr">
+        <is>
+          <t>postMarketChange</t>
+        </is>
+      </c>
+      <c r="FH1" s="1" t="inlineStr">
         <is>
           <t>regularMarketChange</t>
         </is>
       </c>
-      <c r="EX1" s="1" t="inlineStr">
+      <c r="FI1" s="1" t="inlineStr">
         <is>
           <t>regularMarketDayRange</t>
         </is>
       </c>
-      <c r="EY1" s="1" t="inlineStr">
+      <c r="FJ1" s="1" t="inlineStr">
         <is>
           <t>fullExchangeName</t>
         </is>
       </c>
-      <c r="EZ1" s="1" t="inlineStr">
+      <c r="FK1" s="1" t="inlineStr">
         <is>
           <t>averageDailyVolume3Month</t>
         </is>
       </c>
-      <c r="FA1" s="1" t="inlineStr">
+      <c r="FL1" s="1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChange</t>
         </is>
       </c>
-      <c r="FB1" s="1" t="inlineStr">
+      <c r="FM1" s="1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChangePercent</t>
         </is>
       </c>
-      <c r="FC1" s="1" t="inlineStr">
+      <c r="FN1" s="1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekRange</t>
         </is>
       </c>
-      <c r="FD1" s="1" t="inlineStr">
+      <c r="FO1" s="1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChange</t>
         </is>
       </c>
-      <c r="FE1" s="1" t="inlineStr">
+      <c r="FP1" s="1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChangePercent</t>
         </is>
       </c>
-      <c r="FF1" s="1" t="inlineStr">
+      <c r="FQ1" s="1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekChangePercent</t>
         </is>
       </c>
-      <c r="FG1" s="1" t="inlineStr">
+      <c r="FR1" s="1" t="inlineStr">
         <is>
           <t>dividendDate</t>
         </is>
       </c>
-      <c r="FH1" s="1" t="inlineStr">
+      <c r="FS1" s="1" t="inlineStr">
         <is>
           <t>earningsTimestamp</t>
         </is>
       </c>
-      <c r="FI1" s="1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="FJ1" s="1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="FK1" s="1" t="inlineStr">
-        <is>
-          <t>earningsCallTimestampStart</t>
-        </is>
-      </c>
-      <c r="FL1" s="1" t="inlineStr">
-        <is>
-          <t>earningsCallTimestampEnd</t>
-        </is>
-      </c>
-      <c r="FM1" s="1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="FN1" s="1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="FO1" s="1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="FP1" s="1" t="inlineStr">
+      <c r="FT1" s="1" t="inlineStr">
         <is>
           <t>displayName</t>
         </is>
       </c>
-      <c r="FQ1" s="1" t="inlineStr">
+      <c r="FU1" s="1" t="inlineStr">
         <is>
           <t>trailingPegRatio</t>
         </is>
@@ -1410,34 +1430,34 @@
         <v>2</v>
       </c>
       <c r="AC2" t="n">
-        <v>103</v>
+        <v>102.11</v>
       </c>
       <c r="AD2" t="n">
-        <v>103.39</v>
+        <v>102.51</v>
       </c>
       <c r="AE2" t="n">
-        <v>101.824</v>
+        <v>102.65</v>
       </c>
       <c r="AF2" t="n">
-        <v>104.07</v>
+        <v>104.315</v>
       </c>
       <c r="AG2" t="n">
-        <v>103</v>
+        <v>102.11</v>
       </c>
       <c r="AH2" t="n">
-        <v>103.39</v>
+        <v>102.51</v>
       </c>
       <c r="AI2" t="n">
-        <v>101.824</v>
+        <v>102.65</v>
       </c>
       <c r="AJ2" t="n">
-        <v>104.07</v>
+        <v>104.315</v>
       </c>
       <c r="AK2" t="n">
         <v>2.4</v>
       </c>
       <c r="AL2" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="AM2" t="n">
         <v>1754265600</v>
@@ -1452,40 +1472,40 @@
         <v>1.4</v>
       </c>
       <c r="AQ2" t="n">
-        <v>15.05031</v>
+        <v>15.276218</v>
       </c>
       <c r="AR2" t="n">
-        <v>14.171155</v>
+        <v>14.383866</v>
       </c>
       <c r="AS2" t="n">
-        <v>6577510</v>
+        <v>11209900</v>
       </c>
       <c r="AT2" t="n">
-        <v>6577510</v>
+        <v>11209900</v>
       </c>
       <c r="AU2" t="n">
-        <v>14919479</v>
+        <v>14619628</v>
       </c>
       <c r="AV2" t="n">
-        <v>13615270</v>
+        <v>13578920</v>
       </c>
       <c r="AW2" t="n">
-        <v>13615270</v>
+        <v>13578920</v>
       </c>
       <c r="AX2" t="n">
-        <v>102.13</v>
+        <v>103</v>
       </c>
       <c r="AY2" t="n">
-        <v>102.13</v>
+        <v>103.54</v>
       </c>
       <c r="AZ2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="BA2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BB2" t="n">
-        <v>187570192384</v>
+        <v>190385651712</v>
       </c>
       <c r="BC2" t="n">
         <v>55.51</v>
@@ -1500,19 +1520,19 @@
         <v>9.699999999999999</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.575629</v>
+        <v>2.6142895</v>
       </c>
       <c r="BH2" t="n">
-        <v>95.581</v>
+        <v>96.248</v>
       </c>
       <c r="BI2" t="n">
-        <v>79.82335</v>
+        <v>80.27985</v>
       </c>
       <c r="BJ2" t="n">
         <v>2.24</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.021747572</v>
+        <v>0.021937126</v>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
@@ -1523,7 +1543,7 @@
         <v>0</v>
       </c>
       <c r="BN2" t="n">
-        <v>-5330516480</v>
+        <v>-4557339136</v>
       </c>
       <c r="BO2" t="n">
         <v>0.19466999</v>
@@ -1535,40 +1555,40 @@
         <v>1840897898</v>
       </c>
       <c r="BR2" t="n">
-        <v>37121462</v>
+        <v>36260537</v>
       </c>
       <c r="BS2" t="n">
-        <v>36549061</v>
+        <v>40492586</v>
       </c>
       <c r="BT2" t="n">
-        <v>1753920000</v>
+        <v>1755216000</v>
       </c>
       <c r="BU2" t="n">
-        <v>1756425600</v>
+        <v>1757894400</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.0202</v>
+        <v>0.0197</v>
       </c>
       <c r="BW2" t="n">
         <v>0.0023700001</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.79719</v>
+        <v>0.79718</v>
       </c>
       <c r="BY2" t="n">
-        <v>2.74</v>
+        <v>2.84</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0.0202</v>
+        <v>0.0197</v>
       </c>
       <c r="CA2" t="n">
-        <v>1849655568</v>
+        <v>1840897898</v>
       </c>
       <c r="CB2" t="n">
         <v>106.943</v>
       </c>
       <c r="CC2" t="n">
-        <v>0.95275617</v>
+        <v>0.96705717</v>
       </c>
       <c r="CD2" t="n">
         <v>1735603200</v>
@@ -1600,13 +1620,13 @@
         <v>1304899200</v>
       </c>
       <c r="CM2" t="n">
-        <v>-0.073</v>
+        <v>-0.063</v>
       </c>
       <c r="CN2" t="n">
-        <v>0.7058629</v>
+        <v>0.6520767</v>
       </c>
       <c r="CO2" t="n">
-        <v>0.16333759</v>
+        <v>0.1529237</v>
       </c>
       <c r="CP2" t="n">
         <v>0.6</v>
@@ -1620,7 +1640,7 @@
         </is>
       </c>
       <c r="CS2" t="n">
-        <v>101.8906</v>
+        <v>103.42</v>
       </c>
       <c r="CT2" t="n">
         <v>125</v>
@@ -1714,7 +1734,7 @@
       </c>
       <c r="DT2" t="inlineStr">
         <is>
-          <t>Nasdaq Real Time Price</t>
+          <t>Delayed Quote</t>
         </is>
       </c>
       <c r="DU2" t="b">
@@ -1727,172 +1747,184 @@
       </c>
       <c r="DW2" t="inlineStr">
         <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="DX2" t="inlineStr">
+        <is>
+          <t>Citigroup, Inc.</t>
+        </is>
+      </c>
+      <c r="DY2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="DZ2" t="inlineStr">
+        <is>
+          <t>Citigroup Inc.</t>
+        </is>
+      </c>
+      <c r="EA2" t="n">
+        <v>1758931164</v>
+      </c>
+      <c r="EB2" t="n">
+        <v>1758916822</v>
+      </c>
+      <c r="EC2" t="inlineStr">
+        <is>
           <t>NYQ</t>
         </is>
       </c>
-      <c r="DX2" t="inlineStr">
+      <c r="ED2" t="inlineStr">
         <is>
           <t>finmb_391687</t>
         </is>
       </c>
-      <c r="DY2" t="n">
-        <v>101.8906</v>
-      </c>
-      <c r="DZ2" t="n">
-        <v>6.77</v>
-      </c>
-      <c r="EA2" t="n">
-        <v>7.19</v>
-      </c>
-      <c r="EB2" t="n">
-        <v>7.66375</v>
-      </c>
-      <c r="EC2" t="n">
-        <v>13.295136</v>
-      </c>
-      <c r="ED2" t="n">
-        <v>6.309601</v>
-      </c>
-      <c r="EE2" t="n">
-        <v>0.06601313</v>
-      </c>
-      <c r="EF2" t="n">
-        <v>22.067253</v>
+      <c r="EE2" t="inlineStr">
+        <is>
+          <t>America/New_York</t>
+        </is>
+      </c>
+      <c r="EF2" t="inlineStr">
+        <is>
+          <t>EDT</t>
+        </is>
       </c>
       <c r="EG2" t="n">
-        <v>0.2764511</v>
-      </c>
-      <c r="EH2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EI2" t="n">
+        <v>-14400000</v>
+      </c>
+      <c r="EH2" t="inlineStr">
+        <is>
+          <t>us_market</t>
+        </is>
+      </c>
+      <c r="EI2" t="b">
         <v>0</v>
       </c>
-      <c r="EJ2" t="inlineStr">
-        <is>
-          <t>1.9 - Buy</t>
-        </is>
-      </c>
-      <c r="EK2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EL2" t="inlineStr">
-        <is>
-          <t>America/New_York</t>
-        </is>
-      </c>
-      <c r="EM2" t="inlineStr">
-        <is>
-          <t>EDT</t>
-        </is>
+      <c r="EJ2" t="n">
+        <v>1.28293</v>
+      </c>
+      <c r="EK2" t="n">
+        <v>103.42</v>
+      </c>
+      <c r="EL2" t="n">
+        <v>1760445000</v>
+      </c>
+      <c r="EM2" t="n">
+        <v>1760445000</v>
       </c>
       <c r="EN2" t="n">
-        <v>-14400000</v>
-      </c>
-      <c r="EO2" t="inlineStr">
-        <is>
-          <t>us_market</t>
-        </is>
+        <v>1760454000</v>
+      </c>
+      <c r="EO2" t="n">
+        <v>1760454000</v>
       </c>
       <c r="EP2" t="b">
         <v>0</v>
       </c>
       <c r="EQ2" t="n">
-        <v>-1.0770854</v>
-      </c>
-      <c r="ER2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+        <v>6.77</v>
+      </c>
+      <c r="ER2" t="n">
+        <v>7.19</v>
       </c>
       <c r="ES2" t="n">
-        <v>1758740031</v>
-      </c>
-      <c r="ET2" t="inlineStr">
-        <is>
-          <t>REGULAR</t>
-        </is>
-      </c>
-      <c r="EU2" t="b">
+        <v>7.64</v>
+      </c>
+      <c r="ET2" t="n">
+        <v>13.536649</v>
+      </c>
+      <c r="EU2" t="n">
+        <v>7.171997</v>
+      </c>
+      <c r="EV2" t="n">
+        <v>0.074515805</v>
+      </c>
+      <c r="EW2" t="n">
+        <v>23.140152</v>
+      </c>
+      <c r="EX2" t="n">
+        <v>0.2882436</v>
+      </c>
+      <c r="EY2" t="n">
+        <v>15</v>
+      </c>
+      <c r="EZ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA2" t="inlineStr">
+        <is>
+          <t>1.9 - Buy</t>
+        </is>
+      </c>
+      <c r="FB2" t="b">
+        <v>0</v>
+      </c>
+      <c r="FC2" t="b">
         <v>1</v>
       </c>
-      <c r="EV2" t="n">
+      <c r="FD2" t="n">
         <v>221149800000</v>
       </c>
-      <c r="EW2" t="n">
-        <v>-1.1093979</v>
-      </c>
-      <c r="EX2" t="inlineStr">
-        <is>
-          <t>101.824 - 104.07</t>
-        </is>
-      </c>
-      <c r="EY2" t="inlineStr">
+      <c r="FE2" t="n">
+        <v>0.087027624</v>
+      </c>
+      <c r="FF2" t="n">
+        <v>103.51</v>
+      </c>
+      <c r="FG2" t="n">
+        <v>0.09000397</v>
+      </c>
+      <c r="FH2" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="FI2" t="inlineStr">
+        <is>
+          <t>102.65 - 104.315</t>
+        </is>
+      </c>
+      <c r="FJ2" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="EZ2" t="n">
-        <v>14919479</v>
-      </c>
-      <c r="FA2" t="n">
-        <v>46.380604</v>
-      </c>
-      <c r="FB2" t="n">
-        <v>0.83553606</v>
-      </c>
-      <c r="FC2" t="inlineStr">
+      <c r="FK2" t="n">
+        <v>14619628</v>
+      </c>
+      <c r="FL2" t="n">
+        <v>47.91</v>
+      </c>
+      <c r="FM2" t="n">
+        <v>0.8630878</v>
+      </c>
+      <c r="FN2" t="inlineStr">
         <is>
           <t>55.51 - 105.59</t>
         </is>
       </c>
-      <c r="FD2" t="n">
-        <v>-3.6993942</v>
-      </c>
-      <c r="FE2" t="n">
-        <v>-0.03503546</v>
-      </c>
-      <c r="FF2" t="n">
-        <v>70.58629000000001</v>
-      </c>
-      <c r="FG2" t="n">
+      <c r="FO2" t="n">
+        <v>-2.1699982</v>
+      </c>
+      <c r="FP2" t="n">
+        <v>-0.020551171</v>
+      </c>
+      <c r="FQ2" t="n">
+        <v>65.20766999999999</v>
+      </c>
+      <c r="FR2" t="n">
         <v>1755820800</v>
       </c>
-      <c r="FH2" t="n">
+      <c r="FS2" t="n">
         <v>1760445000</v>
       </c>
-      <c r="FI2" t="n">
-        <v>1760445000</v>
-      </c>
-      <c r="FJ2" t="n">
-        <v>1760445000</v>
-      </c>
-      <c r="FK2" t="n">
-        <v>1760454000</v>
-      </c>
-      <c r="FL2" t="n">
-        <v>1760454000</v>
-      </c>
-      <c r="FM2" t="b">
-        <v>0</v>
-      </c>
-      <c r="FN2" t="inlineStr">
-        <is>
-          <t>Citigroup, Inc.</t>
-        </is>
-      </c>
-      <c r="FO2" t="inlineStr">
-        <is>
-          <t>Citigroup Inc.</t>
-        </is>
-      </c>
-      <c r="FP2" t="inlineStr">
+      <c r="FT2" t="inlineStr">
         <is>
           <t>Citigroup</t>
         </is>
       </c>
-      <c r="FQ2" t="n">
-        <v>0.8774999999999999</v>
+      <c r="FU2" t="n">
+        <v>0.8811</v>
       </c>
     </row>
   </sheetData>
